--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
@@ -437,6 +437,16 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.95541</v>
+        <v>16.96277</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69159</v>
+        <v>16.59215</v>
       </c>
       <c r="E2" t="n">
-        <v>16.95656</v>
+        <v>16.74727</v>
       </c>
       <c r="F2" t="n">
-        <v>43.0825</v>
+        <v>41.87248</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05073</v>
+        <v>0.04927</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82153</v>
+        <v>1.84439</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.96313</v>
+        <v>16.95587</v>
       </c>
       <c r="D3" t="n">
-        <v>16.48095</v>
+        <v>16.66043</v>
       </c>
       <c r="E3" t="n">
-        <v>16.94874</v>
+        <v>16.87217</v>
       </c>
       <c r="F3" t="n">
-        <v>42.62752</v>
+        <v>42.58359</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05043</v>
+        <v>0.05173</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88511</v>
+        <v>1.84457</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.58785</v>
+        <v>17.40796</v>
       </c>
       <c r="D4" t="n">
-        <v>16.84253</v>
+        <v>16.55495</v>
       </c>
       <c r="E4" t="n">
-        <v>16.87613</v>
+        <v>16.86329</v>
       </c>
       <c r="F4" t="n">
-        <v>42.82035</v>
+        <v>43.17018</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05059</v>
+        <v>0.05102</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87253</v>
+        <v>1.83979</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.96353</v>
+        <v>16.99188</v>
       </c>
       <c r="D5" t="n">
-        <v>16.8224</v>
+        <v>16.63693</v>
       </c>
       <c r="E5" t="n">
-        <v>16.955</v>
+        <v>16.67715</v>
       </c>
       <c r="F5" t="n">
-        <v>43.40089</v>
+        <v>42.67255</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0506</v>
+        <v>0.05138</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82146</v>
+        <v>1.81917</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.95614</v>
+        <v>17.13635</v>
       </c>
       <c r="D6" t="n">
-        <v>16.93224</v>
+        <v>16.87236</v>
       </c>
       <c r="E6" t="n">
-        <v>16.35126</v>
+        <v>16.90983</v>
       </c>
       <c r="F6" t="n">
-        <v>43.00704</v>
+        <v>42.63198</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05088</v>
+        <v>0.05029</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81186</v>
+        <v>1.8407</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.80837</v>
+        <v>17.23467</v>
       </c>
       <c r="D7" t="n">
-        <v>16.51161</v>
+        <v>16.50744</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66022</v>
+        <v>16.64575</v>
       </c>
       <c r="F7" t="n">
-        <v>42.51769</v>
+        <v>43.12202</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05116</v>
+        <v>0.0515</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81937</v>
+        <v>1.82463</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.73809</v>
+        <v>17.28752</v>
       </c>
       <c r="D8" t="n">
-        <v>16.9322</v>
+        <v>16.70532</v>
       </c>
       <c r="E8" t="n">
-        <v>16.63602</v>
+        <v>17.02061</v>
       </c>
       <c r="F8" t="n">
-        <v>42.51645</v>
+        <v>42.63535</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05061</v>
+        <v>0.05102</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81631</v>
+        <v>1.81331</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.70036</v>
+        <v>17.04673</v>
       </c>
       <c r="D9" t="n">
-        <v>16.55144</v>
+        <v>16.69772</v>
       </c>
       <c r="E9" t="n">
-        <v>16.74928</v>
+        <v>16.86491</v>
       </c>
       <c r="F9" t="n">
-        <v>41.62871</v>
+        <v>42.44338</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05108</v>
+        <v>0.05053</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81081</v>
+        <v>1.82287</v>
       </c>
     </row>
     <row r="10">
@@ -650,33 +660,48 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.93223</v>
+        <v>16.82427</v>
       </c>
       <c r="D10" t="n">
-        <v>16.58881</v>
+        <v>16.4255</v>
       </c>
       <c r="E10" t="n">
-        <v>16.85647</v>
+        <v>16.66605</v>
       </c>
       <c r="F10" t="n">
-        <v>42.89548</v>
+        <v>42.80502</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05036</v>
+        <v>0.05164</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82184</v>
+        <v>1.78742</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -688,14 +713,8 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.59911</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.1324</v>
+          <t>Trace 1</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -704,12 +723,6 @@
           <t>Unit 8</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0.61529</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.11587</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -717,12 +730,6 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0.60233</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.12905</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -730,12 +737,6 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0.61253</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.12843</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -743,12 +744,6 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>0.6223</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.12317</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -756,12 +751,6 @@
           <t>Unit 6</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0.61496</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.1043</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -769,12 +758,6 @@
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>0.60331</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.14135</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -782,12 +765,6 @@
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>0.60763</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.12754</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -795,12 +772,6 @@
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0.60909</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.12724</v>
-      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -856,28 +827,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.74512</v>
+        <v>0.74915</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08097</v>
+        <v>0.08081000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6041299999999999</v>
+        <v>0.61959</v>
       </c>
       <c r="F22" t="n">
-        <v>0.97699</v>
+        <v>0.97814</v>
       </c>
       <c r="G22" t="n">
-        <v>0.10861</v>
+        <v>0.11092</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00768</v>
+        <v>0.00772</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09374</v>
+        <v>0.09506000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.12809</v>
+        <v>0.12791</v>
       </c>
     </row>
     <row r="23">
@@ -887,28 +858,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7648</v>
+        <v>0.75731</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08053</v>
+        <v>0.08298999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6014699999999999</v>
+        <v>0.61176</v>
       </c>
       <c r="F23" t="n">
-        <v>0.96155</v>
+        <v>0.96917</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11041</v>
+        <v>0.11214</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00774</v>
+        <v>0.00772</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09505</v>
+        <v>0.09422</v>
       </c>
       <c r="J23" t="n">
-        <v>0.12583</v>
+        <v>0.12586</v>
       </c>
     </row>
     <row r="24">
@@ -918,28 +889,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7454</v>
+        <v>0.7581599999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08237</v>
+        <v>0.08173999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.61648</v>
+        <v>0.59739</v>
       </c>
       <c r="F24" t="n">
-        <v>0.94247</v>
+        <v>0.96561</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11091</v>
+        <v>0.10683</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00766</v>
+        <v>0.00778</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09569</v>
+        <v>0.09462</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12527</v>
+        <v>0.12549</v>
       </c>
     </row>
     <row r="25">
@@ -949,28 +920,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7464</v>
+        <v>0.76133</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08154</v>
+        <v>0.08222</v>
       </c>
       <c r="E25" t="n">
-        <v>0.61185</v>
+        <v>0.61779</v>
       </c>
       <c r="F25" t="n">
-        <v>0.97065</v>
+        <v>0.97463</v>
       </c>
       <c r="G25" t="n">
-        <v>0.11258</v>
+        <v>0.10777</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0075</v>
+        <v>0.00757</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09356</v>
+        <v>0.09266000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12591</v>
+        <v>0.12626</v>
       </c>
     </row>
     <row r="26">
@@ -980,28 +951,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.74426</v>
+        <v>0.75336</v>
       </c>
       <c r="D26" t="n">
-        <v>0.07932</v>
+        <v>0.08011</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6079599999999999</v>
+        <v>0.61403</v>
       </c>
       <c r="F26" t="n">
-        <v>0.94998</v>
+        <v>0.94974</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10893</v>
+        <v>0.10988</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00764</v>
+        <v>0.00779</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09297</v>
+        <v>0.09497999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12635</v>
+        <v>0.12772</v>
       </c>
     </row>
     <row r="27">
@@ -1011,28 +982,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.73608</v>
+        <v>0.74153</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08158</v>
+        <v>0.08013000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6193</v>
+        <v>0.6039099999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.97578</v>
+        <v>0.96761</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11049</v>
+        <v>0.11078</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00767</v>
+        <v>0.00749</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09202</v>
+        <v>0.09265</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12918</v>
+        <v>0.12582</v>
       </c>
     </row>
     <row r="28">
@@ -1042,28 +1013,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.76379</v>
+        <v>0.73346</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08176</v>
+        <v>0.08028</v>
       </c>
       <c r="E28" t="n">
-        <v>0.62674</v>
+        <v>0.60677</v>
       </c>
       <c r="F28" t="n">
-        <v>0.97006</v>
+        <v>0.97988</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11083</v>
+        <v>0.11054</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00759</v>
+        <v>0.00748</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09375</v>
+        <v>0.09454</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12743</v>
+        <v>0.12928</v>
       </c>
     </row>
     <row r="29">
@@ -1073,28 +1044,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.77342</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08189</v>
+        <v>0.08286</v>
       </c>
       <c r="E29" t="n">
-        <v>0.60585</v>
+        <v>0.61305</v>
       </c>
       <c r="F29" t="n">
-        <v>0.95816</v>
+        <v>0.98672</v>
       </c>
       <c r="G29" t="n">
-        <v>0.10903</v>
+        <v>0.11367</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00777</v>
+        <v>0.00764</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09179</v>
+        <v>0.09072</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12566</v>
+        <v>0.12683</v>
       </c>
     </row>
     <row r="30">
@@ -1104,28 +1075,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.75009</v>
+        <v>0.75782</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08081000000000001</v>
+        <v>0.08386</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6131</v>
+        <v>0.61532</v>
       </c>
       <c r="F30" t="n">
-        <v>0.96293</v>
+        <v>0.99949</v>
       </c>
       <c r="G30" t="n">
-        <v>0.10791</v>
+        <v>0.11029</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00751</v>
+        <v>0.00757</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09479</v>
+        <v>0.09383</v>
       </c>
       <c r="J30" t="n">
-        <v>0.12786</v>
+        <v>0.12651</v>
       </c>
     </row>
   </sheetData>
